--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260817.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260817.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
